--- a/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/SubYearTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/SubYearTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="237">
   <si>
     <t>湖北建科国际工程有限公司分公司{year}年度工资总额统计表</t>
   </si>
@@ -56,7 +56,13 @@
     <t>实缴五险人数</t>
   </si>
   <si>
-    <t>实缴五险一金总额</t>
+    <t>实缴五险总额（元）</t>
+  </si>
+  <si>
+    <t>实缴公积金人数</t>
+  </si>
+  <si>
+    <t>实缴公积金总额（元）</t>
   </si>
   <si>
     <t>1月</t>
@@ -305,43 +311,121 @@
     <t>{data1.sjWxAvgNum}</t>
   </si>
   <si>
-    <t>{data1.sjWxYjAmount1}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount2}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount3}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount4}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount5}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount6}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount7}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount8}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount9}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount10}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount11}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjAmount12}</t>
-  </si>
-  <si>
-    <t>{data1.sjWxYjTotal}</t>
+    <t>{data1.sjWxAmount1}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount2}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount3}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount4}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount5}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount6}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount7}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount8}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount9}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount10}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount11}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxAmount12}</t>
+  </si>
+  <si>
+    <t>{data1.sjWxTotal}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum1}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum2}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum3}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum4}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum5}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum6}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum7}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum8}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum9}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum10}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum11}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjNum12}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAvgNum}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount1}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount2}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount3}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount4}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount5}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount6}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount7}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount8}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount9}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount10}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount11}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjAmount12}</t>
+  </si>
+  <si>
+    <t>{data1.sjGjjTotal}</t>
   </si>
   <si>
     <t>{total.yfGzNum1}</t>
@@ -539,43 +623,121 @@
     <t>{total.sjWxAvgNum}</t>
   </si>
   <si>
-    <t>{total.sjWxYjAmount1}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount2}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount3}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount4}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount5}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount6}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount7}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount8}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount9}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount10}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount11}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjAmount12}</t>
-  </si>
-  <si>
-    <t>{total.sjWxYjTotal}</t>
+    <t>{total.sjWxAmount1}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount2}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount3}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount4}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount5}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount6}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount7}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount8}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount9}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount10}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount11}</t>
+  </si>
+  <si>
+    <t>{total.sjWxAmount12}</t>
+  </si>
+  <si>
+    <t>{total.sjWxTotal}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum1}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum2}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum3}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum4}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum5}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum6}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum7}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum8}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum9}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum10}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum11}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjNum12}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAvgNum}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount1}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount2}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount3}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount4}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount5}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount6}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount7}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount8}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount9}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount10}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount11}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjAmount12}</t>
+  </si>
+  <si>
+    <t>{total.sjGjjTotal}</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1849,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:CC6"/>
+  <dimension ref="A1:DC6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5.5" style="1" customWidth="1"/>
@@ -1700,10 +1862,14 @@
     <col min="68" max="68" width="5.875" style="1" customWidth="1"/>
     <col min="69" max="80" width="4.5" style="1" customWidth="1"/>
     <col min="81" max="81" width="6" style="1" customWidth="1"/>
-    <col min="82" max="16383" width="9" style="1"/>
+    <col min="82" max="93" width="4.75" style="1" customWidth="1"/>
+    <col min="94" max="94" width="5.875" style="1" customWidth="1"/>
+    <col min="95" max="106" width="4.5" style="1" customWidth="1"/>
+    <col min="107" max="107" width="6" style="1" customWidth="1"/>
+    <col min="108" max="16383" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="31" customHeight="1" spans="1:81">
+    <row r="1" s="1" customFormat="1" ht="31" customHeight="1" spans="1:107">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1787,8 +1953,34 @@
       <c r="CA1" s="3"/>
       <c r="CB1" s="3"/>
       <c r="CC1" s="3"/>
+      <c r="CD1" s="3"/>
+      <c r="CE1" s="3"/>
+      <c r="CF1" s="3"/>
+      <c r="CG1" s="3"/>
+      <c r="CH1" s="3"/>
+      <c r="CI1" s="3"/>
+      <c r="CJ1" s="3"/>
+      <c r="CK1" s="3"/>
+      <c r="CL1" s="3"/>
+      <c r="CM1" s="3"/>
+      <c r="CN1" s="3"/>
+      <c r="CO1" s="3"/>
+      <c r="CP1" s="3"/>
+      <c r="CQ1" s="3"/>
+      <c r="CR1" s="3"/>
+      <c r="CS1" s="3"/>
+      <c r="CT1" s="3"/>
+      <c r="CU1" s="3"/>
+      <c r="CV1" s="3"/>
+      <c r="CW1" s="3"/>
+      <c r="CX1" s="3"/>
+      <c r="CY1" s="3"/>
+      <c r="CZ1" s="3"/>
+      <c r="DA1" s="3"/>
+      <c r="DB1" s="3"/>
+      <c r="DC1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:81">
+    <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:107">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1888,735 +2080,999 @@
       <c r="CA2" s="5"/>
       <c r="CB2" s="5"/>
       <c r="CC2" s="14"/>
+      <c r="CD2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE2" s="5"/>
+      <c r="CF2" s="5"/>
+      <c r="CG2" s="5"/>
+      <c r="CH2" s="5"/>
+      <c r="CI2" s="5"/>
+      <c r="CJ2" s="5"/>
+      <c r="CK2" s="5"/>
+      <c r="CL2" s="5"/>
+      <c r="CM2" s="5"/>
+      <c r="CN2" s="5"/>
+      <c r="CO2" s="5"/>
+      <c r="CP2" s="5"/>
+      <c r="CQ2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CR2" s="5"/>
+      <c r="CS2" s="5"/>
+      <c r="CT2" s="5"/>
+      <c r="CU2" s="5"/>
+      <c r="CV2" s="5"/>
+      <c r="CW2" s="5"/>
+      <c r="CX2" s="5"/>
+      <c r="CY2" s="5"/>
+      <c r="CZ2" s="5"/>
+      <c r="DA2" s="5"/>
+      <c r="DB2" s="5"/>
+      <c r="DC2" s="14"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="63" customHeight="1" spans="1:81">
+    <row r="3" s="1" customFormat="1" ht="63" customHeight="1" spans="1:107">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="R3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="S3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="T3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="U3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="V3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="W3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="X3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="Y3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="Z3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="AA3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="S3" s="8" t="s">
+      <c r="AB3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="AE3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="AF3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="AG3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="AH3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="X3" s="8" t="s">
+      <c r="AI3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="Y3" s="8" t="s">
+      <c r="AJ3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Z3" s="8" t="s">
+      <c r="AK3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="AA3" s="8" t="s">
+      <c r="AL3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AB3" s="8" t="s">
+      <c r="AM3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AC3" s="12" t="s">
+      <c r="AN3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AD3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF3" s="8" t="s">
+      <c r="AO3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AG3" s="8" t="s">
+      <c r="AR3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="AH3" s="8" t="s">
+      <c r="AS3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="8" t="s">
+      <c r="AT3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="AJ3" s="8" t="s">
+      <c r="AU3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="AK3" s="8" t="s">
+      <c r="AV3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AL3" s="8" t="s">
+      <c r="AW3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="AM3" s="8" t="s">
+      <c r="AX3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="AN3" s="8" t="s">
+      <c r="AY3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AO3" s="8" t="s">
+      <c r="AZ3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AP3" s="8" t="s">
+      <c r="BA3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="BB3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="AQ3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="AR3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="AS3" s="8" t="s">
+      <c r="BC3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AT3" s="8" t="s">
+      <c r="BE3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="AU3" s="8" t="s">
+      <c r="BF3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AV3" s="8" t="s">
+      <c r="BG3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="AW3" s="8" t="s">
+      <c r="BH3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="AX3" s="8" t="s">
+      <c r="BI3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AY3" s="8" t="s">
+      <c r="BJ3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="AZ3" s="8" t="s">
+      <c r="BK3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="BA3" s="8" t="s">
+      <c r="BL3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="BB3" s="8" t="s">
+      <c r="BM3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="BC3" s="8" t="s">
+      <c r="BN3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="BO3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="BD3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="BE3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="BF3" s="8" t="s">
+      <c r="BP3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="BQ3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="BG3" s="8" t="s">
+      <c r="BR3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="BH3" s="8" t="s">
+      <c r="BS3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="BI3" s="8" t="s">
+      <c r="BT3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="BJ3" s="8" t="s">
+      <c r="BU3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="8" t="s">
+      <c r="BV3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="8" t="s">
+      <c r="BW3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="8" t="s">
+      <c r="BX3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="BN3" s="8" t="s">
+      <c r="BY3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="BO3" s="8" t="s">
+      <c r="BZ3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="BP3" s="12" t="s">
+      <c r="CA3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="BQ3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="BR3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="BS3" s="8" t="s">
+      <c r="CB3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="CC3" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="CD3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="BT3" s="8" t="s">
+      <c r="CE3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="BU3" s="8" t="s">
+      <c r="CF3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="BV3" s="8" t="s">
+      <c r="CG3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="BW3" s="8" t="s">
+      <c r="CH3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="BX3" s="8" t="s">
+      <c r="CI3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="BY3" s="8" t="s">
+      <c r="CJ3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="BZ3" s="8" t="s">
+      <c r="CK3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="CA3" s="8" t="s">
+      <c r="CL3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="CB3" s="8" t="s">
+      <c r="CM3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="CC3" s="15" t="s">
+      <c r="CN3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="CO3" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="CP3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="CQ3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="CR3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="CS3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CT3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="CU3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="CV3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="CW3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="CX3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="CY3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="CZ3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="DA3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="DB3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="DC3" s="15" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="23" customHeight="1" spans="1:81">
+    <row r="4" s="1" customFormat="1" ht="23" customHeight="1" spans="1:107">
       <c r="A4" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB4" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC4" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM4" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN4" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO4" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP4" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AR4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT4" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AV4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW4" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY4" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AZ4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BA4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB4" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="BD4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="BE4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG4" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="BH4" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="BI4" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="BJ4" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL4" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="BM4" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="BN4" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="BO4" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP4" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="BQ4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="BR4" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="BS4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="BT4" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="BU4" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="BV4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="BW4" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="BX4" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BY4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="BZ4" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="CA4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="CB4" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="CC4" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="CD4" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="CE4" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="CF4" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="CG4" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="CH4" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="CI4" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="CJ4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="CK4" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="CL4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="CM4" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="CN4" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="CO4" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="CP4" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="CQ4" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="CR4" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="CS4" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="CT4" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="CU4" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="CV4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="CW4" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="CX4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="CY4" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="CZ4" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="DA4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="DB4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="DC4" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="23" customHeight="1" spans="1:107">
+      <c r="A5" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC4" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF4" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG4" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH4" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI4" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="AJ4" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK4" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AL4" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN4" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="AO4" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AQ4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR4" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AS4" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AT4" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AU4" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AV4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW4" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AX4" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY4" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA4" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="BB4" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="BC4" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="BD4" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE4" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="BF4" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="BG4" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="BH4" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BI4" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="BJ4" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="BK4" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="BL4" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM4" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="BN4" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="BO4" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="BP4" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="BQ4" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="BR4" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="BS4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="BT4" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="BU4" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BV4" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="BW4" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="BX4" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="BY4" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="BZ4" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="CA4" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="CB4" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="CC4" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="23" customHeight="1" spans="1:81">
-      <c r="A5" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="V5" s="11" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="W5" s="11" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="X5" s="11" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="AA5" s="11" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="AB5" s="11" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="AC5" s="11" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="AD5" s="11" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="AE5" s="11" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="AF5" s="11" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="AG5" s="11" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="AH5" s="11" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="AI5" s="11" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="AJ5" s="11" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AK5" s="11" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AL5" s="11" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="AM5" s="11" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="AN5" s="11" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="AO5" s="11" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="AP5" s="11" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="AQ5" s="11" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="AR5" s="11" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="AS5" s="11" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="AT5" s="11" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="AU5" s="11" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="AV5" s="11" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="AW5" s="11" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="AX5" s="11" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="AY5" s="11" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="AZ5" s="11" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="BA5" s="11" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="BB5" s="11" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="BC5" s="11" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="BD5" s="11" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="BE5" s="11" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="BF5" s="11" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="BG5" s="11" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="BH5" s="11" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="BI5" s="11" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="BJ5" s="11" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="BK5" s="11" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="BL5" s="11" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="BM5" s="11" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="BN5" s="11" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="BO5" s="11" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="BP5" s="11" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="BQ5" s="11" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="BR5" s="11" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="BS5" s="11" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="BT5" s="11" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="BU5" s="11" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="BV5" s="11" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="BW5" s="11" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="BX5" s="11" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="BY5" s="11" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="BZ5" s="11" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="CA5" s="11" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="CB5" s="11" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="CC5" s="11" t="s">
-        <v>182</v>
+        <v>210</v>
+      </c>
+      <c r="CD5" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="CE5" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="CF5" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="CG5" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="CH5" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="CI5" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="CJ5" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="CK5" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="CL5" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="CM5" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="CN5" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="CO5" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="CP5" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="CQ5" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="CR5" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS5" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="CT5" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="CU5" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="CV5" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="CW5" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="CX5" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="CY5" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="CZ5" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="DA5" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="DB5" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="DC5" s="11" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="A1:CC1"/>
     <mergeCell ref="D2:P2"/>
     <mergeCell ref="Q2:AC2"/>
@@ -2624,6 +3080,8 @@
     <mergeCell ref="AQ2:BC2"/>
     <mergeCell ref="BD2:BP2"/>
     <mergeCell ref="BQ2:CC2"/>
+    <mergeCell ref="CD2:CP2"/>
+    <mergeCell ref="CQ2:DC2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>

--- a/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/SubYearTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/SubYearTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="345">
   <si>
     <t>湖北建科国际工程有限公司分公司{year}年度工资总额统计表</t>
   </si>
@@ -65,6 +65,18 @@
     <t>实缴公积金总额（元）</t>
   </si>
   <si>
+    <t>应发补偿金人数（人）</t>
+  </si>
+  <si>
+    <t>实发补偿金人数（人）</t>
+  </si>
+  <si>
+    <t>应发补偿金总额（元）</t>
+  </si>
+  <si>
+    <t>实发补偿金总额（元）</t>
+  </si>
+  <si>
     <t>1月</t>
   </si>
   <si>
@@ -428,6 +440,162 @@
     <t>{data1.sjGjjTotal}</t>
   </si>
   <si>
+    <t>{data1.yfBcjNum1}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum2}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum3}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum4}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum5}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum6}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum7}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum8}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum9}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum10}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum11}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjNum12}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAvgNum}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum1}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum2}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum3}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum4}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum5}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum6}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum7}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum8}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum9}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum10}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum11}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjNum12}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAvgNum}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount1}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount2}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount3}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount4}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount5}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount6}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount7}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount8}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount9}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount10}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount11}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjAmount12}</t>
+  </si>
+  <si>
+    <t>{data1.yfBcjTotal}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount1}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount2}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount3}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount4}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount5}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount6}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount7}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount8}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount9}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount10}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount11}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjAmount12}</t>
+  </si>
+  <si>
+    <t>{data1.sfBcjTotal}</t>
+  </si>
+  <si>
     <t>{total.yfGzNum1}</t>
   </si>
   <si>
@@ -738,6 +906,162 @@
   </si>
   <si>
     <t>{total.sjGjjTotal}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum1}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum2}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum3}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum4}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum5}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum6}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum7}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum8}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum9}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum10}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum11}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjNum12}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAvgNum}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum1}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum2}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum3}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum4}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum5}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum6}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum7}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum8}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum9}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum10}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum11}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjNum12}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAvgNum}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount1}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount2}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount3}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount4}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount5}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount6}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount7}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount8}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount9}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount10}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount11}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjAmount12}</t>
+  </si>
+  <si>
+    <t>{total.yfBcjTotal}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount1}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount2}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount3}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount4}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount5}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount6}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount7}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount8}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount9}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount10}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount11}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjAmount12}</t>
+  </si>
+  <si>
+    <t>{total.sfBcjTotal}</t>
   </si>
 </sst>
 </file>
@@ -1489,7 +1813,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1498,7 +1822,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1515,6 +1839,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1524,11 +1851,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1849,7 +2176,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:DC6"/>
+  <dimension ref="A1:FC6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5.5" style="1" customWidth="1"/>
@@ -1866,10 +2193,14 @@
     <col min="94" max="94" width="5.875" style="1" customWidth="1"/>
     <col min="95" max="106" width="4.5" style="1" customWidth="1"/>
     <col min="107" max="107" width="6" style="1" customWidth="1"/>
-    <col min="108" max="16383" width="9" style="1"/>
+    <col min="108" max="119" width="5.5" style="1" customWidth="1"/>
+    <col min="120" max="120" width="7.05" style="1" customWidth="1"/>
+    <col min="121" max="146" width="5" style="1" customWidth="1"/>
+    <col min="147" max="159" width="4.75" style="1" customWidth="1"/>
+    <col min="160" max="16383" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="31" customHeight="1" spans="1:107">
+    <row r="1" s="1" customFormat="1" ht="31" customHeight="1" spans="1:159">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1979,8 +2310,60 @@
       <c r="DA1" s="3"/>
       <c r="DB1" s="3"/>
       <c r="DC1" s="3"/>
+      <c r="DD1" s="3"/>
+      <c r="DE1" s="3"/>
+      <c r="DF1" s="3"/>
+      <c r="DG1" s="3"/>
+      <c r="DH1" s="3"/>
+      <c r="DI1" s="3"/>
+      <c r="DJ1" s="3"/>
+      <c r="DK1" s="3"/>
+      <c r="DL1" s="3"/>
+      <c r="DM1" s="3"/>
+      <c r="DN1" s="3"/>
+      <c r="DO1" s="3"/>
+      <c r="DP1" s="3"/>
+      <c r="DQ1" s="3"/>
+      <c r="DR1" s="3"/>
+      <c r="DS1" s="3"/>
+      <c r="DT1" s="3"/>
+      <c r="DU1" s="3"/>
+      <c r="DV1" s="3"/>
+      <c r="DW1" s="3"/>
+      <c r="DX1" s="3"/>
+      <c r="DY1" s="3"/>
+      <c r="DZ1" s="3"/>
+      <c r="EA1" s="3"/>
+      <c r="EB1" s="3"/>
+      <c r="EC1" s="3"/>
+      <c r="ED1" s="3"/>
+      <c r="EE1" s="3"/>
+      <c r="EF1" s="3"/>
+      <c r="EG1" s="3"/>
+      <c r="EH1" s="3"/>
+      <c r="EI1" s="3"/>
+      <c r="EJ1" s="3"/>
+      <c r="EK1" s="3"/>
+      <c r="EL1" s="3"/>
+      <c r="EM1" s="3"/>
+      <c r="EN1" s="3"/>
+      <c r="EO1" s="3"/>
+      <c r="EP1" s="3"/>
+      <c r="EQ1" s="3"/>
+      <c r="ER1" s="3"/>
+      <c r="ES1" s="3"/>
+      <c r="ET1" s="3"/>
+      <c r="EU1" s="3"/>
+      <c r="EV1" s="3"/>
+      <c r="EW1" s="3"/>
+      <c r="EX1" s="3"/>
+      <c r="EY1" s="3"/>
+      <c r="EZ1" s="3"/>
+      <c r="FA1" s="3"/>
+      <c r="FB1" s="3"/>
+      <c r="FC1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:107">
+    <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:159">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2079,7 +2462,7 @@
       <c r="BZ2" s="5"/>
       <c r="CA2" s="5"/>
       <c r="CB2" s="5"/>
-      <c r="CC2" s="14"/>
+      <c r="CC2" s="15"/>
       <c r="CD2" s="5" t="s">
         <v>10</v>
       </c>
@@ -2109,971 +2492,1499 @@
       <c r="CZ2" s="5"/>
       <c r="DA2" s="5"/>
       <c r="DB2" s="5"/>
-      <c r="DC2" s="14"/>
+      <c r="DC2" s="15"/>
+      <c r="DD2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="DE2" s="6"/>
+      <c r="DF2" s="6"/>
+      <c r="DG2" s="6"/>
+      <c r="DH2" s="6"/>
+      <c r="DI2" s="6"/>
+      <c r="DJ2" s="6"/>
+      <c r="DK2" s="6"/>
+      <c r="DL2" s="6"/>
+      <c r="DM2" s="6"/>
+      <c r="DN2" s="6"/>
+      <c r="DO2" s="6"/>
+      <c r="DP2" s="6"/>
+      <c r="DQ2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DR2" s="6"/>
+      <c r="DS2" s="6"/>
+      <c r="DT2" s="6"/>
+      <c r="DU2" s="6"/>
+      <c r="DV2" s="6"/>
+      <c r="DW2" s="6"/>
+      <c r="DX2" s="6"/>
+      <c r="DY2" s="6"/>
+      <c r="DZ2" s="6"/>
+      <c r="EA2" s="6"/>
+      <c r="EB2" s="6"/>
+      <c r="EC2" s="6"/>
+      <c r="ED2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="EE2" s="5"/>
+      <c r="EF2" s="5"/>
+      <c r="EG2" s="5"/>
+      <c r="EH2" s="5"/>
+      <c r="EI2" s="5"/>
+      <c r="EJ2" s="5"/>
+      <c r="EK2" s="5"/>
+      <c r="EL2" s="5"/>
+      <c r="EM2" s="5"/>
+      <c r="EN2" s="5"/>
+      <c r="EO2" s="5"/>
+      <c r="EP2" s="5"/>
+      <c r="EQ2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="ER2" s="5"/>
+      <c r="ES2" s="5"/>
+      <c r="ET2" s="5"/>
+      <c r="EU2" s="5"/>
+      <c r="EV2" s="5"/>
+      <c r="EW2" s="5"/>
+      <c r="EX2" s="5"/>
+      <c r="EY2" s="5"/>
+      <c r="EZ2" s="5"/>
+      <c r="FA2" s="5"/>
+      <c r="FB2" s="5"/>
+      <c r="FC2" s="5"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="63" customHeight="1" spans="1:107">
+    <row r="3" s="1" customFormat="1" ht="63" customHeight="1" spans="1:159">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="R3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="S3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="T3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="U3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="V3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="W3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="X3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="Y3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Q3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="U3" s="8" t="s">
+      <c r="Z3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="AE3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="AF3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="X3" s="8" t="s">
+      <c r="AG3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Y3" s="8" t="s">
+      <c r="AH3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="Z3" s="8" t="s">
+      <c r="AI3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AA3" s="8" t="s">
+      <c r="AJ3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AB3" s="8" t="s">
+      <c r="AK3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="AC3" s="12" t="s">
+      <c r="AL3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AD3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH3" s="8" t="s">
+      <c r="AM3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="AQ3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="AI3" s="8" t="s">
+      <c r="AR3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AJ3" s="8" t="s">
+      <c r="AS3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="AK3" s="8" t="s">
+      <c r="AT3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="AL3" s="8" t="s">
+      <c r="AU3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AM3" s="8" t="s">
+      <c r="AV3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="8" t="s">
+      <c r="AW3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AO3" s="8" t="s">
+      <c r="AX3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="AP3" s="8" t="s">
+      <c r="AY3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AZ3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AQ3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="AR3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AS3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AU3" s="8" t="s">
+      <c r="BA3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="BB3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="BD3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="AV3" s="8" t="s">
+      <c r="BE3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AW3" s="8" t="s">
+      <c r="BF3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="AX3" s="8" t="s">
+      <c r="BG3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="AY3" s="8" t="s">
+      <c r="BH3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AZ3" s="8" t="s">
+      <c r="BI3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="BA3" s="8" t="s">
+      <c r="BJ3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="BB3" s="8" t="s">
+      <c r="BK3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="BC3" s="8" t="s">
+      <c r="BL3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="BM3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="BD3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="BE3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="BF3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="BG3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="BH3" s="8" t="s">
+      <c r="BN3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="BO3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="BQ3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="BI3" s="8" t="s">
+      <c r="BR3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="BJ3" s="8" t="s">
+      <c r="BS3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="BK3" s="8" t="s">
+      <c r="BT3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="BL3" s="8" t="s">
+      <c r="BU3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="BM3" s="8" t="s">
+      <c r="BV3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="BN3" s="8" t="s">
+      <c r="BW3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="BO3" s="8" t="s">
+      <c r="BX3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="BP3" s="12" t="s">
+      <c r="BY3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="BQ3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="BR3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="BS3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="BT3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="BU3" s="8" t="s">
+      <c r="BZ3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="CA3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="CB3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="CC3" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="CD3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="BV3" s="8" t="s">
+      <c r="CE3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="BW3" s="8" t="s">
+      <c r="CF3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="BX3" s="8" t="s">
+      <c r="CG3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="BY3" s="8" t="s">
+      <c r="CH3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="BZ3" s="8" t="s">
+      <c r="CI3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="CA3" s="8" t="s">
+      <c r="CJ3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="CB3" s="8" t="s">
+      <c r="CK3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="CC3" s="15" t="s">
+      <c r="CL3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="CM3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="CD3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="CE3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="CF3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="CG3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="CH3" s="8" t="s">
+      <c r="CN3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="CO3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="CP3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="CQ3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="CI3" s="8" t="s">
+      <c r="CR3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="CJ3" s="8" t="s">
+      <c r="CS3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="CK3" s="8" t="s">
+      <c r="CT3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="CL3" s="8" t="s">
+      <c r="CU3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="CM3" s="8" t="s">
+      <c r="CV3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="CN3" s="8" t="s">
+      <c r="CW3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="CO3" s="8" t="s">
+      <c r="CX3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="CP3" s="12" t="s">
+      <c r="CY3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="CQ3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="CR3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="CS3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="CT3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="CU3" s="8" t="s">
+      <c r="CZ3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="DA3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="DB3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC3" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="DD3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="CV3" s="8" t="s">
+      <c r="DE3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="CW3" s="8" t="s">
+      <c r="DF3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="CX3" s="8" t="s">
+      <c r="DG3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="CY3" s="8" t="s">
+      <c r="DH3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="CZ3" s="8" t="s">
+      <c r="DI3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="DA3" s="8" t="s">
+      <c r="DJ3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="DB3" s="8" t="s">
+      <c r="DK3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="DC3" s="15" t="s">
+      <c r="DL3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="DM3" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="DN3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="DO3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="DP3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="DQ3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="DR3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="DS3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="DT3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="DU3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="DV3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="DW3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="DX3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="DY3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="DZ3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="EA3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="EB3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="ED3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="EE3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="EF3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="EG3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="EH3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="EI3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="EJ3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="EK3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="EL3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="EM3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="EN3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="EO3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="EP3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="ER3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="ES3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="ET3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="EU3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="EV3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="EW3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="EX3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="EY3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="EZ3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="FA3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="FB3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="FC3" s="8" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="23" customHeight="1" spans="1:107">
+    <row r="4" s="1" customFormat="1" ht="23" customHeight="1" spans="1:159">
       <c r="A4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI4" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK4" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP4" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS4" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU4" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AV4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX4" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY4" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AZ4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="BA4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="BB4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC4" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="BD4" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="BE4" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="BF4" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="BG4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="BH4" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="BI4" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ4" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="BK4" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL4" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="BM4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="BN4" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="BP4" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="BQ4" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="BR4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="BS4" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="BT4" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BU4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV4" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="BW4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="BX4" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="BY4" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="BZ4" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="CA4" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="CB4" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="CC4" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="CD4" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="CE4" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="CF4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="CG4" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="CH4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="CI4" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="CJ4" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="CK4" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="CL4" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="CM4" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="CN4" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="CO4" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="CP4" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="CQ4" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="CR4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="CS4" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="CT4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="CU4" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV4" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="CW4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="CX4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="CY4" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="CZ4" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="DA4" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="DB4" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="DC4" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="DD4" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="DE4" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="DF4" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="DG4" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="DH4" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="DI4" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="DJ4" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="DK4" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="DL4" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="DM4" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="DN4" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="DO4" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="DP4" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="DQ4" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="DR4" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="DS4" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="DT4" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="DU4" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="DV4" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="DW4" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="DX4" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="DY4" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ4" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="EA4" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="EB4" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="EC4" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="ED4" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="EE4" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="EF4" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="EG4" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="EH4" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="EI4" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="EJ4" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="EK4" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="EL4" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="EM4" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="EN4" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="EO4" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="EP4" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="EQ4" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="ER4" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="ES4" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="ET4" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="EU4" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="EV4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="EW4" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="EX4" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY4" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="EZ4" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="FA4" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="FB4" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="FC4" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="23" customHeight="1" spans="1:159">
+      <c r="A5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB4" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE4" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF4" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG4" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH4" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI4" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ4" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AL4" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM4" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP4" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ4" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AR4" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS4" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="AU4" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AV4" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW4" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY4" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AZ4" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="BA4" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BB4" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="BC4" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="BD4" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="BE4" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="BF4" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BG4" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="BH4" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="BI4" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="BJ4" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="BK4" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="BL4" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="BM4" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="BN4" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="BO4" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="BP4" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="BQ4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="BR4" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="BS4" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT4" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="BU4" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="BV4" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="BW4" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="BX4" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="BY4" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BZ4" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="CA4" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="CB4" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="CC4" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="CD4" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="CE4" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="CF4" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG4" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH4" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI4" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="CJ4" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="CK4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="CL4" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="CM4" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="CN4" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="CO4" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="CP4" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="CQ4" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="CR4" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="CS4" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="CT4" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="CU4" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="CV4" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="CW4" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="CX4" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="CY4" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="CZ4" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="DA4" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="DB4" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="DC4" s="13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="23" customHeight="1" spans="1:107">
-      <c r="A5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="T5" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="U5" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="V5" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="W5" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="X5" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y5" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z5" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA5" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB5" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC5" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="AD5" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE5" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="AF5" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="AG5" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH5" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI5" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="AJ5" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="AK5" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL5" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="AM5" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="AN5" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="AO5" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="AP5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AQ5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AR5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="AS5" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="AT5" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="AU5" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="AV5" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="AW5" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="AX5" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="AY5" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="AZ5" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="BA5" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="BB5" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="BC5" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="BD5" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="BE5" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="BF5" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="BG5" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="BH5" s="11" t="s">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="BI5" s="11" t="s">
+      <c r="E5" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="BJ5" s="11" t="s">
+      <c r="F5" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="BK5" s="11" t="s">
+      <c r="G5" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="BL5" s="11" t="s">
+      <c r="H5" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="BM5" s="11" t="s">
+      <c r="I5" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="BN5" s="11" t="s">
+      <c r="J5" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="BO5" s="11" t="s">
+      <c r="K5" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="BP5" s="11" t="s">
+      <c r="L5" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="BQ5" s="11" t="s">
+      <c r="M5" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="BR5" s="11" t="s">
+      <c r="N5" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="BS5" s="11" t="s">
+      <c r="O5" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="BT5" s="11" t="s">
+      <c r="P5" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="BU5" s="11" t="s">
+      <c r="Q5" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="BV5" s="11" t="s">
+      <c r="R5" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="BW5" s="11" t="s">
+      <c r="S5" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="BX5" s="11" t="s">
+      <c r="T5" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="BY5" s="11" t="s">
+      <c r="U5" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="BZ5" s="11" t="s">
+      <c r="V5" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="CA5" s="11" t="s">
+      <c r="W5" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="CB5" s="11" t="s">
+      <c r="X5" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="CC5" s="11" t="s">
+      <c r="Y5" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="CD5" s="11" t="s">
+      <c r="Z5" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="CE5" s="11" t="s">
+      <c r="AA5" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="CF5" s="11" t="s">
+      <c r="AB5" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="CG5" s="11" t="s">
+      <c r="AC5" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="CH5" s="11" t="s">
+      <c r="AD5" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="CI5" s="11" t="s">
+      <c r="AE5" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="CJ5" s="11" t="s">
+      <c r="AF5" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="CK5" s="11" t="s">
+      <c r="AG5" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="CL5" s="11" t="s">
+      <c r="AH5" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="CM5" s="11" t="s">
+      <c r="AI5" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="CN5" s="11" t="s">
+      <c r="AJ5" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="CO5" s="11" t="s">
+      <c r="AK5" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="CP5" s="11" t="s">
+      <c r="AL5" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="CQ5" s="11" t="s">
+      <c r="AM5" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="CR5" s="11" t="s">
+      <c r="AN5" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="CS5" s="11" t="s">
+      <c r="AO5" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="CT5" s="11" t="s">
+      <c r="AP5" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="CU5" s="11" t="s">
+      <c r="AQ5" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="CV5" s="11" t="s">
+      <c r="AR5" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="CW5" s="11" t="s">
+      <c r="AS5" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="CX5" s="11" t="s">
+      <c r="AT5" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="CY5" s="11" t="s">
+      <c r="AU5" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="CZ5" s="11" t="s">
+      <c r="AV5" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="DA5" s="11" t="s">
+      <c r="AW5" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="DB5" s="11" t="s">
+      <c r="AX5" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="DC5" s="11" t="s">
+      <c r="AY5" s="13" t="s">
         <v>236</v>
+      </c>
+      <c r="AZ5" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="BA5" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="BB5" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="BC5" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="BD5" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="BE5" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="BF5" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="BG5" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="BH5" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="BI5" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="BJ5" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="BK5" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="BL5" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="BM5" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="BN5" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO5" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="BP5" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="BQ5" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="BR5" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS5" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="BT5" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="BU5" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="BV5" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="BW5" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="BX5" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="BY5" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="BZ5" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="CA5" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="CB5" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="CC5" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="CD5" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="CE5" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="CF5" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="CG5" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH5" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI5" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="CJ5" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="CK5" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="CL5" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="CM5" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="CN5" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="CO5" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="CP5" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="CQ5" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="CR5" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="CS5" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="CT5" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="CU5" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="CV5" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="CW5" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="CX5" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="CY5" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="CZ5" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="DA5" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="DB5" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="DC5" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="DD5" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="DE5" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="DF5" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="DG5" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="DH5" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="DI5" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="DJ5" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="DK5" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="DL5" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="DM5" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="DN5" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="DO5" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="DP5" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="DQ5" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="DR5" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="DS5" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="DT5" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="DU5" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="DV5" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="DW5" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="DX5" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="DY5" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="DZ5" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="EA5" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="EB5" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="EC5" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="ED5" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="EE5" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="EF5" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="EG5" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="EH5" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="EI5" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="EJ5" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="EK5" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="EL5" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="EM5" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="EN5" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="EO5" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="EP5" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="EQ5" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="ER5" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="ES5" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="ET5" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="EU5" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="EV5" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="EW5" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="EX5" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="EY5" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="EZ5" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="FA5" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="FB5" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="FC5" s="13" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1"/>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A1:CC1"/>
+  <mergeCells count="17">
+    <mergeCell ref="A1:FC1"/>
     <mergeCell ref="D2:P2"/>
     <mergeCell ref="Q2:AC2"/>
     <mergeCell ref="AD2:AP2"/>
@@ -3082,6 +3993,10 @@
     <mergeCell ref="BQ2:CC2"/>
     <mergeCell ref="CD2:CP2"/>
     <mergeCell ref="CQ2:DC2"/>
+    <mergeCell ref="DD2:DP2"/>
+    <mergeCell ref="DQ2:EC2"/>
+    <mergeCell ref="ED2:EP2"/>
+    <mergeCell ref="EQ2:FC2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
